--- a/slot-project/docs/math_spec.xlsx
+++ b/slot-project/docs/math_spec.xlsx
@@ -792,7 +792,7 @@
     <t xml:space="preserve">Simulation Results (SDK slotsim)</t>
   </si>
   <si>
-    <t xml:space="preserve">Source: slotsim report / math neon_fortune v1.0.0 / generated 2026-09-23T12:11:03Z. Values are pasted from the SDK output (they don't recalculate). After changing the math, rerun make_specs.sh.</t>
+    <t xml:space="preserve">Source: slotsim report / math neon_fortune v1.0.0 / generated 2026-09-23T12:24:05Z. Values are pasted from the SDK output (they don't recalculate). After changing the math, rerun make_specs.sh.</t>
   </si>
   <si>
     <t xml:space="preserve">Monte Carlo</t>
@@ -1666,11 +1666,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="79108661"/>
-        <c:axId val="89996411"/>
+        <c:axId val="9024966"/>
+        <c:axId val="65690480"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="79108661"/>
+        <c:axId val="9024966"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1736,7 +1736,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89996411"/>
+        <c:crossAx val="65690480"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1744,7 +1744,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="89996411"/>
+        <c:axId val="65690480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1820,7 +1820,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79108661"/>
+        <c:crossAx val="9024966"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
